--- a/loss-time/outputs/Loss_time_05-10_den_21-10.xlsx
+++ b/loss-time/outputs/Loss_time_05-10_den_21-10.xlsx
@@ -42,7 +42,7 @@
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 17-10'!$A$2:$Q$40</definedName>
     <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 19-10'!$A$2:$Q$42</definedName>
     <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 20-10'!$A$2:$Q$43</definedName>
-    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 21-10'!$A$2:$Q$40</definedName>
+    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 21-10'!$A$2:$Q$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4991" uniqueCount="331">
   <si>
     <t xml:space="preserve">LOSS TIME WHITE WOOD - 05/10/2026</t>
   </si>
@@ -913,10 +913,13 @@
     <t xml:space="preserve">Ngày cuối A2 (không tính CN)</t>
   </si>
   <si>
-    <t xml:space="preserve">20/10</t>
+    <t xml:space="preserve">21/10</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/10</t>
   </si>
   <si>
     <t xml:space="preserve">A2 ngày 1</t>
@@ -1033,7 +1036,7 @@
     <t xml:space="preserve">Ngày 09/10 có 8 nhân viên mới (Assembly 6, Raw Cutting Panel 2; lấy theo P22 đã nhập trên hệ thống), A2 bắt đầu từ 10/10. Ngày 10/10 chưa thấy có nhân viên mới (chờ xác nhận).</t>
   </si>
   <si>
-    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Ngày 21/10 chưa có nhân viên mới (chờ báo). Thứ Hai 19/10, Thứ Ba 20/10 và Thứ Tư 21/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
+    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Ngày 21/10 có 5 nhân viên mới (Raw Cutting Panel 1, Machining 2, Assembly 2 gồm 1 người dưới Mr.Dũng-Inlay). Thứ Hai 19/10, Thứ Ba 20/10 và Thứ Tư 21/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
   </si>
   <si>
     <t xml:space="preserve">Thứ Bảy 10/10 không tăng ca: P26 và P20 Assembly ghi 7:30-15:30 (sớm 30 phút so với ca ngày thường 7:30-16:00); 4 dòng P20 ngắn ghi 7:00-7:30 theo mặc định, chờ xác nhận.</t>
@@ -13338,7 +13341,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -14367,147 +14370,141 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="str">
+      <c r="A23" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B23,21)</f>
         <v>W43</v>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="9" t="n">
         <v>46316</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="M23" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N23" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O23" s="17" t="n">
+      <c r="K23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O23" s="12" t="n">
         <f aca="false">(N23-M23)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P23" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q23" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="12" t="n">
         <f aca="false">P23*O23</f>
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="str">
+      <c r="A24" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B24,21)</f>
         <v>W43</v>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="9" t="n">
         <v>46316</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="13" t="s">
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="M24" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="K24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="10"/>
+      <c r="M24" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O24" s="12" t="n">
         <f aca="false">(N24-M24)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P24" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" s="17" t="n">
+      <c r="Q24" s="12" t="n">
         <f aca="false">P24*O24</f>
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="str">
+      <c r="A25" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B25,21)</f>
         <v>W43</v>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="9" t="n">
         <v>46316</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="13" t="s">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K25" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="L25" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="M25" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N25" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O25" s="17" t="n">
+      <c r="K25" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="10"/>
+      <c r="M25" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O25" s="12" t="n">
         <f aca="false">(N25-M25)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="12" t="n">
         <f aca="false">P25*O25</f>
-        <v>4.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14523,7 +14520,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>52</v>
@@ -14535,10 +14532,10 @@
         <v>50</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>0.3125</v>
@@ -14551,11 +14548,11 @@
         <v>4.5</v>
       </c>
       <c r="P26" s="13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q26" s="17" t="n">
         <f aca="false">P26*O26</f>
-        <v>13.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14571,7 +14568,7 @@
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
       <c r="G27" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>52</v>
@@ -14583,10 +14580,10 @@
         <v>50</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>0.3125</v>
@@ -14599,11 +14596,11 @@
         <v>4.5</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="17" t="n">
         <f aca="false">P27*O27</f>
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14631,10 +14628,10 @@
         <v>50</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>0.3125</v>
@@ -14647,11 +14644,11 @@
         <v>4.5</v>
       </c>
       <c r="P28" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28*O28</f>
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14667,7 +14664,7 @@
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
       <c r="G29" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>52</v>
@@ -14679,10 +14676,10 @@
         <v>50</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>0.3125</v>
@@ -14695,11 +14692,11 @@
         <v>4.5</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29*O29</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14715,7 +14712,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
       <c r="G30" s="13" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>52</v>
@@ -14727,10 +14724,10 @@
         <v>50</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>0.3125</v>
@@ -14743,11 +14740,11 @@
         <v>4.5</v>
       </c>
       <c r="P30" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="17" t="n">
         <f aca="false">P30*O30</f>
-        <v>4.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14763,7 +14760,7 @@
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
       <c r="G31" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>52</v>
@@ -14775,10 +14772,10 @@
         <v>50</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>0.3125</v>
@@ -14811,7 +14808,7 @@
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
       <c r="G32" s="13" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>52</v>
@@ -14823,10 +14820,10 @@
         <v>50</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M32" s="16" t="n">
         <v>0.3125</v>
@@ -14839,11 +14836,11 @@
         <v>4.5</v>
       </c>
       <c r="P32" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="17" t="n">
         <f aca="false">P32*O32</f>
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14859,7 +14856,7 @@
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
       <c r="G33" s="13" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>52</v>
@@ -14871,10 +14868,10 @@
         <v>50</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M33" s="16" t="n">
         <v>0.3125</v>
@@ -14919,10 +14916,10 @@
         <v>50</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M34" s="16" t="n">
         <v>0.3125</v>
@@ -14935,11 +14932,11 @@
         <v>4.5</v>
       </c>
       <c r="P34" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="17" t="n">
         <f aca="false">P34*O34</f>
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14955,7 +14952,7 @@
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
       <c r="G35" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>52</v>
@@ -14967,10 +14964,10 @@
         <v>50</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M35" s="16" t="n">
         <v>0.3125</v>
@@ -15003,7 +15000,7 @@
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>52</v>
@@ -15015,10 +15012,10 @@
         <v>50</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M36" s="16" t="n">
         <v>0.3125</v>
@@ -15063,10 +15060,10 @@
         <v>50</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>233</v>
+        <v>187</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="M37" s="16" t="n">
         <v>0.3125</v>
@@ -15079,11 +15076,11 @@
         <v>4.5</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="17" t="n">
         <f aca="false">P37*O37</f>
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15099,7 +15096,7 @@
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>52</v>
@@ -15111,10 +15108,10 @@
         <v>50</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M38" s="16" t="n">
         <v>0.3125</v>
@@ -15127,11 +15124,11 @@
         <v>4.5</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q38" s="17" t="n">
         <f aca="false">P38*O38</f>
-        <v>4.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15159,10 +15156,10 @@
         <v>50</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="M39" s="16" t="n">
         <v>0.3125</v>
@@ -15175,11 +15172,11 @@
         <v>4.5</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="17" t="n">
         <f aca="false">P39*O39</f>
-        <v>18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15195,7 +15192,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>52</v>
@@ -15207,10 +15204,10 @@
         <v>50</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M40" s="16" t="n">
         <v>0.3125</v>
@@ -15231,21 +15228,165 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P41" s="18" t="s">
+      <c r="A41" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B41,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="M41" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N41" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <f aca="false">(N41-M41)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="17" t="n">
+        <f aca="false">P41*O41</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B42,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="M42" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <f aca="false">(N42-M42)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P42" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <f aca="false">P42*O42</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B43,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="M43" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N43" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <f aca="false">(N43-M43)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="17" t="n">
+        <f aca="false">P43*O43</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P44" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="Q41" s="19" t="n">
-        <f aca="false">SUM(Q3:Q40)</f>
-        <v>474.5</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
+      <c r="Q44" s="19" t="n">
+        <f aca="false">SUM(Q3:Q43)</f>
+        <v>514.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q40"/>
+  <autoFilter ref="A2:Q43"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -18610,31 +18751,31 @@
         <v>20</v>
       </c>
       <c r="C131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,C$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,C$130)</f>
         <v>3.5</v>
       </c>
       <c r="D131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,D$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,D$130)</f>
         <v>9</v>
       </c>
       <c r="E131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,E$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,E$130)</f>
         <v>9.5</v>
       </c>
       <c r="F131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,F$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,F$130)</f>
         <v>25</v>
       </c>
       <c r="G131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,G$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,G$130)</f>
         <v>0</v>
       </c>
       <c r="H131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,H$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,H$130)</f>
         <v>0</v>
       </c>
       <c r="I131" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A131,'Loss time 21-10'!$G$3:$G$40,I$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A131,'Loss time 21-10'!$G$3:$G$43,I$130)</f>
         <v>0</v>
       </c>
       <c r="J131" s="24" t="n">
@@ -18650,31 +18791,31 @@
         <v>31</v>
       </c>
       <c r="C132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,C$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,C$130)</f>
         <v>12.5</v>
       </c>
       <c r="D132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,D$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,D$130)</f>
         <v>112.5</v>
       </c>
       <c r="E132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,E$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,E$130)</f>
         <v>75</v>
       </c>
       <c r="F132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,F$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,F$130)</f>
         <v>25</v>
       </c>
       <c r="G132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,G$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,G$130)</f>
         <v>0</v>
       </c>
       <c r="H132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,H$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,H$130)</f>
         <v>0</v>
       </c>
       <c r="I132" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A132,'Loss time 21-10'!$G$3:$G$40,I$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A132,'Loss time 21-10'!$G$3:$G$43,I$130)</f>
         <v>0</v>
       </c>
       <c r="J132" s="24" t="n">
@@ -18690,36 +18831,36 @@
         <v>49</v>
       </c>
       <c r="C133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,C$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,C$130)</f>
         <v>0</v>
       </c>
       <c r="D133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,D$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,D$130)</f>
         <v>0</v>
       </c>
       <c r="E133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,E$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,E$130)</f>
+        <v>16</v>
+      </c>
+      <c r="F133" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,F$130)</f>
+        <v>16</v>
+      </c>
+      <c r="G133" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,G$130)</f>
         <v>0</v>
       </c>
-      <c r="F133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,F$130)</f>
-        <v>0</v>
-      </c>
-      <c r="G133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,G$130)</f>
-        <v>0</v>
-      </c>
       <c r="H133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,H$130)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,H$130)</f>
+        <v>8</v>
       </c>
       <c r="I133" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A133,'Loss time 21-10'!$G$3:$G$40,I$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A133,'Loss time 21-10'!$G$3:$G$43,I$130)</f>
         <v>0</v>
       </c>
       <c r="J133" s="24" t="n">
         <f aca="false">SUM(C133:I133)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18730,31 +18871,31 @@
         <v>53</v>
       </c>
       <c r="C134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,C$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,C$130)</f>
         <v>0</v>
       </c>
       <c r="D134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,D$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,D$130)</f>
         <v>0</v>
       </c>
       <c r="E134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,E$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,E$130)</f>
         <v>31.5</v>
       </c>
       <c r="F134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,F$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,F$130)</f>
         <v>126</v>
       </c>
       <c r="G134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,G$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,G$130)</f>
         <v>0</v>
       </c>
       <c r="H134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,H$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,H$130)</f>
         <v>45</v>
       </c>
       <c r="I134" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$40,'Loss time 21-10'!$H$3:$H$40,$A134,'Loss time 21-10'!$G$3:$G$40,I$130)</f>
+        <f aca="false">SUMIFS('Loss time 21-10'!$Q$3:$Q$43,'Loss time 21-10'!$H$3:$H$43,$A134,'Loss time 21-10'!$G$3:$G$43,I$130)</f>
         <v>0</v>
       </c>
       <c r="J134" s="24" t="n">
@@ -18777,11 +18918,11 @@
       </c>
       <c r="E135" s="24" t="n">
         <f aca="false">SUM(E131:E134)</f>
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F135" s="24" t="n">
         <f aca="false">SUM(F131:F134)</f>
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G135" s="24" t="n">
         <f aca="false">SUM(G131:G134)</f>
@@ -18789,7 +18930,7 @@
       </c>
       <c r="H135" s="24" t="n">
         <f aca="false">SUM(H131:H134)</f>
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I135" s="24" t="n">
         <f aca="false">SUM(I131:I134)</f>
@@ -18797,7 +18938,7 @@
       </c>
       <c r="J135" s="24" t="n">
         <f aca="false">SUM(J131:J134)</f>
-        <v>474.5</v>
+        <v>514.5</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18821,7 +18962,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -18900,10 +19041,10 @@
         <v>285</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>286</v>
@@ -18945,14 +19086,14 @@
         <v>286</v>
       </c>
       <c r="Q4" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="R4" s="8" t="s">
-        <v>287</v>
-      </c>
       <c r="S4" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,20),12,11)</f>
-        <v>46329</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,21),12,11)</f>
+        <v>46330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19005,1450 +19146,1450 @@
         <v>286</v>
       </c>
       <c r="Q5" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="S5" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,21),12,11)</f>
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,21),12,11)</f>
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="S5" s="26" t="n">
+      <c r="B7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="S7" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,20),12,11)</f>
         <v>46329</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="S8" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,20),12,11)</f>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Q6" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="S6" s="26" t="n">
+      <c r="Q9" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="S9" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,19),12,11)</f>
         <v>46328</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="S7" s="26" t="n">
+      <c r="R10" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="S10" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,19),12,11)</f>
         <v>46328</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="R8" s="8" t="s">
+      <c r="Q11" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="S8" s="26" t="n">
+      <c r="R11" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="S11" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,16),12,11)</f>
         <v>46325</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="S9" s="26" t="n">
+      <c r="R12" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="S12" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,15),12,11)</f>
         <v>46324</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q13" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="S10" s="26" t="n">
+      <c r="R13" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="S13" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,14),12,11)</f>
         <v>46323</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="S11" s="26" t="n">
+      <c r="R14" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="S14" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
         <v>46322</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q15" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="S12" s="26" t="n">
+      <c r="R15" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="S15" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
         <v>46322</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="S13" s="26" t="n">
+      <c r="R16" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="S16" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
         <v>46322</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q17" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="S14" s="26" t="n">
+      <c r="R17" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="S17" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,12),12,11)</f>
         <v>46321</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q18" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="S15" s="26" t="n">
+      <c r="R18" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="S18" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,12),12,11)</f>
         <v>46321</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="P19" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="R16" s="8" t="s">
+      <c r="Q19" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="S16" s="26" t="n">
+      <c r="R19" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="S19" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,9),12,11)</f>
         <v>46318</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="R17" s="8" t="s">
+      <c r="Q20" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="S17" s="26" t="n">
+      <c r="R20" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="S20" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,9),12,11)</f>
         <v>46318</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q21" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="S18" s="26" t="n">
+      <c r="R21" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="S21" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,8),12,11)</f>
         <v>46317</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q22" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="S19" s="26" t="n">
+      <c r="R22" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="S22" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,8),12,11)</f>
         <v>46317</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q23" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="S20" s="26" t="n">
+      <c r="R23" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="S23" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,7),12,11)</f>
         <v>46316</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q24" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="S21" s="26" t="n">
+      <c r="R24" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="S24" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,7),12,11)</f>
         <v>46316</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q25" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="S22" s="26" t="n">
+      <c r="R25" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="S25" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
         <v>46315</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q26" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="S23" s="26" t="n">
+      <c r="R26" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="S26" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
         <v>46315</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q27" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="S24" s="26" t="n">
+      <c r="R27" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="S27" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
         <v>46315</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q28" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="S25" s="26" t="n">
+      <c r="R28" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="S28" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),12,11)</f>
         <v>46314</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="N26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="O26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="S26" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="P27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="R27" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="S27" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="S28" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
-      </c>
-    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S29" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -20457,7 +20598,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>28</v>
@@ -20466,109 +20607,109 @@
         <v>3</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S30" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),6,11)</f>
-        <v>46307</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
+        <v>46302</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S31" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -20577,58 +20718,58 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S32" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -20637,118 +20778,118 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D33" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>309</v>
-      </c>
       <c r="H33" s="13" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S33" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
-        <v>46302</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),6,11)</f>
+        <v>46307</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S34" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -20757,58 +20898,58 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S35" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -20817,118 +20958,118 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R36" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S36" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
+        <v>46302</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R37" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S37" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -20937,58 +21078,58 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S38" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -21006,49 +21147,49 @@
         <v>1</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R39" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S39" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -21057,62 +21198,62 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O40" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P40" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q40" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R40" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S40" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),8,11)</f>
-        <v>46309</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21120,99 +21261,279 @@
         <v>314</v>
       </c>
       <c r="B41" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="S41" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="P42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="S42" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B43" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="J41" s="13" t="s">
+      <c r="C43" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="K41" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="L41" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="M41" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="N41" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="O41" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="P41" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q41" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="R41" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="S41" s="27" t="n">
+      <c r="J43" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="M43" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="O43" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="P43" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q43" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="R43" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="S43" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),8,11)</f>
         <v>46309</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
-        <v>319</v>
-      </c>
-    </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
-        <v>321</v>
+      <c r="A44" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="P44" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q44" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="R44" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="S44" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),8,11)</f>
+        <v>46309</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20" t="s">
         <v>326</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -21231,7 +21552,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -21242,7 +21563,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21256,48 +21577,48 @@
         <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
@@ -21360,7 +21681,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>28</v>
@@ -21423,7 +21744,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>72</v>
@@ -21486,7 +21807,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>25</v>
@@ -21549,7 +21870,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>28</v>
@@ -21612,7 +21933,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>72</v>
@@ -21675,7 +21996,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>72</v>
@@ -21738,7 +22059,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>25</v>
@@ -21801,7 +22122,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>28</v>
@@ -21864,7 +22185,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>72</v>
@@ -21927,7 +22248,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>28</v>
@@ -21990,7 +22311,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>72</v>
@@ -22053,7 +22374,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>28</v>
@@ -22116,7 +22437,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>72</v>
@@ -22179,7 +22500,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
@@ -22242,7 +22563,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>28</v>
@@ -22305,7 +22626,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>28</v>
@@ -22368,7 +22689,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>28</v>
@@ -22431,7 +22752,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>28</v>
@@ -22494,7 +22815,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>25</v>
@@ -22557,7 +22878,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>28</v>
@@ -22620,7 +22941,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>25</v>
@@ -22681,9 +23002,198 @@
         <v>46329</v>
       </c>
     </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <f aca="false">DATE(2026,10,21)</f>
+        <v>46316</v>
+      </c>
+      <c r="E26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D26,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E26,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F26,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="H26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G26,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H26,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="J26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I26,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="K26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J26,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="L26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K26,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="M26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L26,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M26,1,11)</f>
+        <v>46328</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N26,1,11)</f>
+        <v>46329</v>
+      </c>
+      <c r="P26" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O26,1,11)</f>
+        <v>46330</v>
+      </c>
+    </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
-        <v>329</v>
+      <c r="A27" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <f aca="false">DATE(2026,10,21)</f>
+        <v>46316</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D27,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E27,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F27,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G27,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H27,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="J27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I27,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="K27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J27,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="L27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K27,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="M27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L27,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M27,1,11)</f>
+        <v>46328</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N27,1,11)</f>
+        <v>46329</v>
+      </c>
+      <c r="P27" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O27,1,11)</f>
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <f aca="false">DATE(2026,10,21)</f>
+        <v>46316</v>
+      </c>
+      <c r="E28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D28,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E28,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F28,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G28,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H28,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="J28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I28,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="K28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J28,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="L28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K28,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="M28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L28,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M28,1,11)</f>
+        <v>46328</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N28,1,11)</f>
+        <v>46329</v>
+      </c>
+      <c r="P28" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O28,1,11)</f>
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
